--- a/300.xlsx
+++ b/300.xlsx
@@ -511,7 +511,7 @@
         <v>0.4524632692337036</v>
       </c>
       <c r="K2" t="n">
-        <v>1.523850000012317e-05</v>
+        <v>1.587500000005093e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.4351803958415985</v>
       </c>
       <c r="K3" t="n">
-        <v>9.845599997788667e-06</v>
+        <v>1.006919999963429e-05</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.447928249835968</v>
       </c>
       <c r="K4" t="n">
-        <v>1.018130000011297e-05</v>
+        <v>9.856800000306975e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.4653018116950989</v>
       </c>
       <c r="K5" t="n">
-        <v>1.05130999982066e-05</v>
+        <v>9.841600000072503e-06</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.446069210767746</v>
       </c>
       <c r="K6" t="n">
-        <v>1.009359999807202e-05</v>
+        <v>1.065139999991516e-05</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.4901336133480072</v>
       </c>
       <c r="K7" t="n">
-        <v>1.026329999876907e-05</v>
+        <v>9.81599999977334e-06</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.4944420158863068</v>
       </c>
       <c r="K8" t="n">
-        <v>9.861599999567262e-06</v>
+        <v>9.720900000502298e-06</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.4927139282226562</v>
       </c>
       <c r="K9" t="n">
-        <v>9.833599997364217e-06</v>
+        <v>9.727699999530159e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.496104896068573</v>
       </c>
       <c r="K10" t="n">
-        <v>9.804399996937719e-06</v>
+        <v>1.154570000016975e-05</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.4914999008178711</v>
       </c>
       <c r="K11" t="n">
-        <v>1.002640000297106e-05</v>
+        <v>9.81210000009014e-06</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.4931358695030212</v>
       </c>
       <c r="K12" t="n">
-        <v>9.634599999117199e-06</v>
+        <v>9.663799999543699e-06</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.4937478005886078</v>
       </c>
       <c r="K13" t="n">
-        <v>1.048179999997956e-05</v>
+        <v>9.456800000407385e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.496439665555954</v>
       </c>
       <c r="K14" t="n">
-        <v>9.745199997269082e-06</v>
+        <v>9.990399999878719e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.4954337775707245</v>
       </c>
       <c r="K15" t="n">
-        <v>1.032560000021476e-05</v>
+        <v>9.927300000526884e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.4957082271575928</v>
       </c>
       <c r="K16" t="n">
-        <v>1.080930000171065e-05</v>
+        <v>9.553199999572826e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.4611021280288696</v>
       </c>
       <c r="K17" t="n">
-        <v>2.230290000079549e-05</v>
+        <v>2.384150000034424e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.4966996610164642</v>
       </c>
       <c r="K18" t="n">
-        <v>2.318030000242288e-05</v>
+        <v>2.340860000003886e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.4683510661125183</v>
       </c>
       <c r="K19" t="n">
-        <v>2.280270000119344e-05</v>
+        <v>2.153209999960382e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.5770438313484192</v>
       </c>
       <c r="K20" t="n">
-        <v>2.467690000048606e-05</v>
+        <v>2.416320000065752e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.461920827627182</v>
       </c>
       <c r="K21" t="n">
-        <v>2.520799999911105e-05</v>
+        <v>2.291319999949337e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.7016832232475281</v>
       </c>
       <c r="K22" t="n">
-        <v>2.214879999883124e-05</v>
+        <v>2.089129999967554e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.6908981204032898</v>
       </c>
       <c r="K23" t="n">
-        <v>2.478070000142907e-05</v>
+        <v>2.434170000015001e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.6801029443740845</v>
       </c>
       <c r="K24" t="n">
-        <v>2.553840000109631e-05</v>
+        <v>2.423550000003161e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.6816705465316772</v>
       </c>
       <c r="K25" t="n">
-        <v>2.329570000074455e-05</v>
+        <v>2.169630000025791e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.7020230889320374</v>
       </c>
       <c r="K26" t="n">
-        <v>2.38418000008096e-05</v>
+        <v>2.307389999987208e-05</v>
       </c>
     </row>
   </sheetData>
